--- a/calcul_cycle_pixel.xlsx
+++ b/calcul_cycle_pixel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\minis\Documents\HEIA_FR\Master\Advanced_hardware_design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{664E6F74-03A8-4D38-A75C-FBF269E047FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC45BCA5-430E-4B6F-9687-215D8A96EAC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-1044" yWindow="-17388" windowWidth="30936" windowHeight="17496" xr2:uid="{B580467B-BE93-4B89-9B37-A1FB2DBFC3C5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="72">
   <si>
     <t>Nbre_pixels</t>
   </si>
@@ -210,13 +210,55 @@
   </si>
   <si>
     <t>CI grayscale (sans decimation sur sobel)</t>
+  </si>
+  <si>
+    <t>nbre_cycles sobel complete : 2921688</t>
+  </si>
+  <si>
+    <t>nbre_cycles conv greyscale : 908676</t>
+  </si>
+  <si>
+    <t>sobel+gray image 320x240 avec CI grayscale calcul 4pixels a la fois</t>
+  </si>
+  <si>
+    <t>sobel+gray image 320x240 avec CI grayscale calcul 4pixels a la fois loop unrolling complet</t>
+  </si>
+  <si>
+    <t>sobel+gray image 320x240 avec CI grayscale calcul 4pixels a la fois loop unrolling complet &amp; funroll-loops flag</t>
+  </si>
+  <si>
+    <t>finline-functions flag (déjà enabled à O3)</t>
+  </si>
+  <si>
+    <t>https://gcc.gnu.org/onlinedocs/gcc/Optimize-Options.html</t>
+  </si>
+  <si>
+    <t>faggressive-loop-optimizations</t>
+  </si>
+  <si>
+    <t>si commente fonction pas utilise</t>
+  </si>
+  <si>
+    <t>sobel+gray sur image 320x240 avec CI grayscale calcul 4pixels a la fois</t>
+  </si>
+  <si>
+    <t>Sobel+gray sur image 320x240 avec CI grayscale 1 pixel à la fois</t>
+  </si>
+  <si>
+    <t>sobel+gray image 320x240 avec CI grayscale calcul 4pixels a la fois loop unrolling complet &amp; funroll-loops flag &amp; finline-functions</t>
+  </si>
+  <si>
+    <t>sobel+gray image 320x240 avec loop unrolling complet sur x (grayscale 4 pixel à la fois)</t>
+  </si>
+  <si>
+    <t>sobel + gray sur image 320x240 avec loop unrolling complet sur x (grayscale 1 pixel à la fois)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -232,8 +274,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -258,6 +306,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -271,7 +325,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -286,12 +340,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="11" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="11" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -307,6 +362,111 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>98353</xdr:colOff>
+      <xdr:row>202</xdr:row>
+      <xdr:rowOff>57466</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>1739154</xdr:colOff>
+      <xdr:row>233</xdr:row>
+      <xdr:rowOff>58214</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Image 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{368B9F29-903C-95D5-7BF6-12899C024C9C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14473031" y="36633466"/>
+          <a:ext cx="9913344" cy="5604698"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>2140984</xdr:colOff>
+      <xdr:row>201</xdr:row>
+      <xdr:rowOff>148344</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>1205984</xdr:colOff>
+      <xdr:row>258</xdr:row>
+      <xdr:rowOff>63252</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Image 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D1874E5-7E39-6838-0918-EA989F592180}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="24807255" y="36543530"/>
+          <a:ext cx="18097220" cy="10225091"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -626,10 +786,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99A453B8-5D5B-4238-8F52-35105F746F78}">
-  <dimension ref="A2:AK176"/>
+  <dimension ref="A2:AN274"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="92.90625" customWidth="1"/>
+    <col min="1" max="1" width="107.1796875" customWidth="1"/>
     <col min="2" max="2" width="34.7265625" customWidth="1"/>
     <col min="3" max="3" width="17.08984375" customWidth="1"/>
     <col min="4" max="4" width="18.36328125" customWidth="1"/>
@@ -759,7 +919,7 @@
       <c r="A7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="11">
         <f>1/50000000</f>
         <v>2E-8</v>
       </c>
@@ -1044,6 +1204,11 @@
         <v>16.890487670898438</v>
       </c>
     </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>64</v>
+      </c>
+    </row>
     <row r="16" spans="1:37" x14ac:dyDescent="0.35">
       <c r="P16">
         <f>(P8+P9)*(1/50000000)</f>
@@ -1277,6 +1442,9 @@
       <c r="D23">
         <v>102474052</v>
       </c>
+      <c r="AI23" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="s">
@@ -1290,6 +1458,9 @@
         <f>D21+D22+D23</f>
         <v>1546815084</v>
       </c>
+      <c r="AI24" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="25" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B25" s="4" t="s">
@@ -1325,7 +1496,7 @@
         <f>1/(C25*$B$7)</f>
         <v>0.45228589588496271</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27" s="4">
         <f>1/(D25*$B$7)</f>
         <v>3.0246253173099636E-2</v>
       </c>
@@ -1361,16 +1532,31 @@
       <c r="D32">
         <v>537526338</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="AI32" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="1:40" x14ac:dyDescent="0.35">
       <c r="B33" s="3" t="s">
         <v>31</v>
       </c>
       <c r="D33">
         <v>103250395</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="AI33">
+        <v>2945696</v>
+      </c>
+      <c r="AK33">
+        <v>10761391</v>
+      </c>
+      <c r="AM33" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN33">
+        <v>10532456</v>
+      </c>
+    </row>
+    <row r="34" spans="1:40" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>30</v>
       </c>
@@ -1378,8 +1564,17 @@
         <f>D31+D32+D33</f>
         <v>1177743512</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="AI34">
+        <v>904321</v>
+      </c>
+      <c r="AK34">
+        <v>3146390</v>
+      </c>
+      <c r="AN34">
+        <v>3124367</v>
+      </c>
+    </row>
+    <row r="35" spans="1:40" x14ac:dyDescent="0.35">
       <c r="B35" s="4" t="s">
         <v>34</v>
       </c>
@@ -1389,7 +1584,7 @@
         <v>1283694277</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:40" x14ac:dyDescent="0.35">
       <c r="B36" s="4" t="s">
         <v>35</v>
       </c>
@@ -1399,22 +1594,27 @@
         <v>6529.2067311604815</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:40" x14ac:dyDescent="0.35">
       <c r="B37" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C37" s="8"/>
-      <c r="D37" s="13">
+      <c r="D37" s="12">
         <f>1/(D35*$B$7)</f>
         <v>3.8950084062733578E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:40" x14ac:dyDescent="0.35">
       <c r="B38" s="6"/>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="AI39" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
         <v>42</v>
       </c>
@@ -1425,23 +1625,35 @@
         <v>106098183</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:40" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D41">
         <v>421850202</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="AI41">
+        <v>2921759</v>
+      </c>
+      <c r="AK41">
+        <v>10911106</v>
+      </c>
+    </row>
+    <row r="42" spans="1:40" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D42">
         <v>421864723</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="AI42">
+        <v>705283</v>
+      </c>
+      <c r="AK42">
+        <v>4557063</v>
+      </c>
+    </row>
+    <row r="43" spans="1:40" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>31</v>
       </c>
@@ -1449,7 +1661,7 @@
         <v>102949870</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:40" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
         <v>30</v>
       </c>
@@ -1458,7 +1670,7 @@
         <v>946664795</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:40" x14ac:dyDescent="0.35">
       <c r="B45" s="4" t="s">
         <v>34</v>
       </c>
@@ -1468,7 +1680,7 @@
         <v>1052762978</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:40" x14ac:dyDescent="0.35">
       <c r="B46" s="4" t="s">
         <v>35</v>
       </c>
@@ -1478,17 +1690,36 @@
         <v>5354.6294047037763</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:40" x14ac:dyDescent="0.35">
       <c r="B47" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C47" s="8"/>
-      <c r="D47" s="13">
+      <c r="D47" s="12">
         <f>1/(D45*$B$7)</f>
         <v>4.7494071357817066E-2</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="AI47" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="48" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="AI48">
+        <v>2521850</v>
+      </c>
+      <c r="AK48">
+        <v>10911181</v>
+      </c>
+    </row>
+    <row r="49" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="AI49">
+        <v>679229</v>
+      </c>
+      <c r="AK49">
+        <v>4559515</v>
+      </c>
+    </row>
+    <row r="50" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A50" s="9" t="s">
         <v>43</v>
       </c>
@@ -1499,7 +1730,7 @@
         <v>154756745</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B51" s="3" t="s">
         <v>28</v>
       </c>
@@ -1507,7 +1738,7 @@
         <v>351853397</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B52" s="3" t="s">
         <v>29</v>
       </c>
@@ -1515,7 +1746,7 @@
         <v>348055958</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B53" s="3" t="s">
         <v>31</v>
       </c>
@@ -1523,7 +1754,7 @@
         <v>102552347</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B54" s="3" t="s">
         <v>30</v>
       </c>
@@ -1531,8 +1762,11 @@
         <f>D51+D52+D53</f>
         <v>802461702</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="AI54" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="55" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B55" s="4" t="s">
         <v>34</v>
       </c>
@@ -1541,8 +1775,14 @@
         <f>SUM(D50:D53)</f>
         <v>957218447</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="AI55">
+        <v>2506232</v>
+      </c>
+      <c r="AK55">
+        <v>10887822</v>
+      </c>
+    </row>
+    <row r="56" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B56" s="4" t="s">
         <v>35</v>
       </c>
@@ -1551,18 +1791,27 @@
         <f>D55/$B$6</f>
         <v>4868.6647898356123</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="AI56">
+        <v>682008</v>
+      </c>
+      <c r="AK56">
+        <v>4639731</v>
+      </c>
+    </row>
+    <row r="57" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B57" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C57" s="8"/>
-      <c r="D57" s="13">
+      <c r="D57" s="12">
         <f>1/(D55*$B$7)</f>
         <v>5.223468076352273E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:37" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="AI59" s="13"/>
+    </row>
+    <row r="60" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A60" s="9" t="s">
         <v>44</v>
       </c>
@@ -1573,15 +1822,18 @@
         <v>154756745</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B61" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D61">
         <v>669978092</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="AI61" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="62" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B62" s="4" t="s">
         <v>34</v>
       </c>
@@ -1590,8 +1842,14 @@
         <f>SUM(D60:D61)</f>
         <v>824734837</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="AI62">
+        <v>2505195</v>
+      </c>
+      <c r="AK62">
+        <v>10896776</v>
+      </c>
+    </row>
+    <row r="63" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B63" s="4" t="s">
         <v>35</v>
       </c>
@@ -1600,13 +1858,19 @@
         <f>D62/$B$6</f>
         <v>4194.8183034261065</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="AI63">
+        <v>683176</v>
+      </c>
+      <c r="AK63">
+        <v>4585281</v>
+      </c>
+    </row>
+    <row r="64" spans="1:37" x14ac:dyDescent="0.35">
       <c r="B64" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C64" s="8"/>
-      <c r="D64" s="13">
+      <c r="D64" s="12">
         <f>1/(D62*$B$7)</f>
         <v>6.0625546244507666E-2</v>
       </c>
@@ -1666,11 +1930,11 @@
       <c r="B71" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C71" s="13">
+      <c r="C71" s="12">
         <f>1/(C69*$B$7)</f>
         <v>0.79619180821178848</v>
       </c>
-      <c r="D71" s="13">
+      <c r="D71" s="12">
         <f>1/(D69*$B$7)</f>
         <v>0.14595978967182632</v>
       </c>
@@ -1718,11 +1982,11 @@
       <c r="B78" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C78" s="13">
+      <c r="C78" s="12">
         <f>1/(C76*$B$7)</f>
         <v>1.8808822240454239</v>
       </c>
-      <c r="D78" s="11"/>
+      <c r="D78" s="10"/>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" s="9" t="s">
@@ -1765,7 +2029,7 @@
       <c r="B85" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C85" s="13">
+      <c r="C85" s="12">
         <f>1/(C83*$B$7)</f>
         <v>2.1565894417866636</v>
       </c>
@@ -1811,7 +2075,7 @@
       <c r="B92" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C92" s="13">
+      <c r="C92" s="12">
         <f>1/(C90*$B$7)</f>
         <v>2.1733251117893237</v>
       </c>
@@ -1857,7 +2121,7 @@
       <c r="B99" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C99" s="13">
+      <c r="C99" s="12">
         <f>1/(C97*$B$7)</f>
         <v>2.2230108476704937</v>
       </c>
@@ -1903,7 +2167,7 @@
       <c r="B106" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C106" s="13">
+      <c r="C106" s="12">
         <f>1/(C104*$B$7)</f>
         <v>2.2165122895410496</v>
       </c>
@@ -1949,7 +2213,7 @@
       <c r="B113" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C113" s="13">
+      <c r="C113" s="12">
         <f>1/(C111*$B$7)</f>
         <v>3.1973144604813211</v>
       </c>
@@ -1995,7 +2259,7 @@
       <c r="B120" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C120" s="13">
+      <c r="C120" s="12">
         <f>1/(C118*$B$7)</f>
         <v>1.8160871762524955</v>
       </c>
@@ -2041,7 +2305,7 @@
       <c r="B127" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C127" s="13">
+      <c r="C127" s="12">
         <f>1/(C125*$B$7)</f>
         <v>2.1191382939478767</v>
       </c>
@@ -2087,7 +2351,7 @@
       <c r="B134" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C134" s="13">
+      <c r="C134" s="12">
         <f>1/(C132*$B$7)</f>
         <v>3.5174072262739626</v>
       </c>
@@ -2133,7 +2397,7 @@
       <c r="B141" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C141" s="13">
+      <c r="C141" s="12">
         <f>1/(C139*$B$7)</f>
         <v>6.9759009131872851</v>
       </c>
@@ -2179,7 +2443,7 @@
       <c r="B148" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C148" s="13">
+      <c r="C148" s="12">
         <f>1/(C146*$B$7)</f>
         <v>4.4602038313150905</v>
       </c>
@@ -2225,7 +2489,7 @@
       <c r="B155" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C155" s="13">
+      <c r="C155" s="12">
         <f>1/(C153*$B$7)</f>
         <v>3.9897609965593093</v>
       </c>
@@ -2271,7 +2535,7 @@
       <c r="B162" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C162" s="13">
+      <c r="C162" s="12">
         <f>1/(C160*$B$7)</f>
         <v>5.0675673963659662</v>
       </c>
@@ -2317,7 +2581,7 @@
       <c r="B169" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C169" s="13">
+      <c r="C169" s="12">
         <f>1/(C167*$B$7)</f>
         <v>11.257701393523309</v>
       </c>
@@ -2363,12 +2627,687 @@
       <c r="B176" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C176" s="8">
+      <c r="C176" s="12">
         <f>1/(C174*$B$7)</f>
         <v>5.0890139791142799</v>
       </c>
     </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A179" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C179">
+        <v>7875645</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B180" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C180">
+        <v>2209818</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B181" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C181" s="4">
+        <f>SUM(C179:C180)</f>
+        <v>10085463</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B182" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C182" s="4">
+        <f>C181/$B$6</f>
+        <v>51.297317504882813</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B183" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C183" s="12">
+        <f>1/(C181*$B$7)</f>
+        <v>4.9576306015896341</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A186" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C186">
+        <v>7643014</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B187" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C187">
+        <v>2234900</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B188" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C188" s="4">
+        <f>SUM(C186:C187)</f>
+        <v>9877914</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B189" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C189" s="4">
+        <f>C188/$B$6</f>
+        <v>50.241668701171875</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B190" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C190" s="12">
+        <f>1/(C188*$B$7)</f>
+        <v>5.061797460475967</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A193" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C193">
+        <v>7623525</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B194" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C194">
+        <v>2072816</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B195" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C195" s="4">
+        <f>SUM(C193:C194)</f>
+        <v>9696341</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B196" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C196" s="4">
+        <f>C195/$B$6</f>
+        <v>49.318140665690102</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B197" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C197" s="12">
+        <f>1/(C195*$B$7)</f>
+        <v>5.1565843239217761</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A200" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C200">
+        <v>7586948</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B201" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C201">
+        <v>2266619</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B202" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C202" s="4">
+        <f>SUM(C200:C201)</f>
+        <v>9853567</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B203" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C203" s="4">
+        <f>C202/$B$6</f>
+        <v>50.117833455403648</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B204" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C204" s="12">
+        <f>1/(C202*$B$7)</f>
+        <v>5.0743045640223485</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A207" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C207">
+        <v>7604944</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B208" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C208">
+        <v>2194123</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B209" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C209" s="4">
+        <f>SUM(C207:C208)</f>
+        <v>9799067</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B210" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C210" s="4">
+        <f>C209/$B$6</f>
+        <v>49.840632120768227</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B211" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C211" s="12">
+        <f>1/(C209*$B$7)</f>
+        <v>5.1025265976852694</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A214" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C214">
+        <v>2927796</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B215" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C215">
+        <v>877405</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B216" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C216" s="4">
+        <f>SUM(C214:C215)</f>
+        <v>3805201</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B217" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C217" s="4">
+        <f>C216/$B$6</f>
+        <v>19.35425313313802</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B218" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C218" s="12">
+        <f>1/(C216*$B$7)</f>
+        <v>13.139910349019669</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A221" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C221">
+        <v>2945696</v>
+      </c>
+      <c r="D221">
+        <v>10761391</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B222" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C222">
+        <v>904321</v>
+      </c>
+      <c r="D222">
+        <v>3146390</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B223" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C223" s="4">
+        <f>SUM(C221:C222)</f>
+        <v>3850017</v>
+      </c>
+      <c r="D223" s="4">
+        <f>SUM(D221:D222)</f>
+        <v>13907781</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B224" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C224" s="4">
+        <f>C223/$B$6</f>
+        <v>19.582199096679688</v>
+      </c>
+      <c r="D224" s="4">
+        <f>D223/$B$6</f>
+        <v>70.738632202148438</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B225" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C225" s="12">
+        <f>1/(C223*$B$7)</f>
+        <v>12.986955642014049</v>
+      </c>
+      <c r="D225" s="12">
+        <f>1/(D223*$B$7)</f>
+        <v>3.5951098165839683</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A228" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C228">
+        <v>2881913</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B229" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C229">
+        <v>778470</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B230" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C230" s="4">
+        <f>SUM(C228:C229)</f>
+        <v>3660383</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B231" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C231" s="4">
+        <f>C230/$B$6</f>
+        <v>18.61767069498698</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B232" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C232" s="12">
+        <f>1/(C230*$B$7)</f>
+        <v>13.659772761484248</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A235" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B235" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C235">
+        <v>2921759</v>
+      </c>
+      <c r="D235">
+        <v>10911106</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B236" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C236">
+        <v>705283</v>
+      </c>
+      <c r="D236">
+        <v>4557063</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B237" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C237" s="4">
+        <f>SUM(C235:C236)</f>
+        <v>3627042</v>
+      </c>
+      <c r="D237" s="4">
+        <f>SUM(D235:D236)</f>
+        <v>15468169</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B238" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C238" s="4">
+        <f>C237/$B$6</f>
+        <v>18.448089599609375</v>
+      </c>
+      <c r="D238" s="4">
+        <f>D237/$B$6</f>
+        <v>78.675175984700516</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B239" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C239" s="12">
+        <f>1/(C237*$B$7)</f>
+        <v>13.785338024759572</v>
+      </c>
+      <c r="D239" s="12">
+        <f>1/(D237*$B$7)</f>
+        <v>3.232444641637934</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A242" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C242">
+        <v>2521850</v>
+      </c>
+      <c r="D242">
+        <v>10911181</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B243" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C243">
+        <v>679229</v>
+      </c>
+      <c r="D243">
+        <v>4559515</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B244" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C244" s="4">
+        <f>SUM(C242:C243)</f>
+        <v>3201079</v>
+      </c>
+      <c r="D244" s="4">
+        <f>SUM(D242:D243)</f>
+        <v>15470696</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B245" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C245" s="4">
+        <f>C244/$B$6</f>
+        <v>16.281529744466145</v>
+      </c>
+      <c r="D245" s="4">
+        <f>D244/$B$6</f>
+        <v>78.688028971354171</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B246" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C246" s="12">
+        <f>1/(C244*$B$7)</f>
+        <v>15.619733221204477</v>
+      </c>
+      <c r="D246" s="12">
+        <f>1/(D244*$B$7)</f>
+        <v>3.2319166506794521</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A249" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B249" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C249">
+        <v>2506232</v>
+      </c>
+      <c r="D249">
+        <v>10887822</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B250" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C250">
+        <v>682008</v>
+      </c>
+      <c r="D250">
+        <v>4639731</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B251" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C251" s="4">
+        <f>SUM(C249:C250)</f>
+        <v>3188240</v>
+      </c>
+      <c r="D251" s="4">
+        <f>SUM(D249:D250)</f>
+        <v>15527553</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B252" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C252" s="4">
+        <f>C251/$B$6</f>
+        <v>16.216227213541668</v>
+      </c>
+      <c r="D252" s="4">
+        <f>D251/$B$6</f>
+        <v>78.977218627929688</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B253" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C253" s="14">
+        <f>1/(C251*$B$7)</f>
+        <v>15.682633678769479</v>
+      </c>
+      <c r="D253" s="14">
+        <f>1/(D251*$B$7)</f>
+        <v>3.2200823916041377</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B256" s="6"/>
+      <c r="C256" s="7"/>
+      <c r="D256" s="7"/>
+    </row>
+    <row r="257" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B257" s="6"/>
+      <c r="C257" s="7"/>
+      <c r="D257" s="7"/>
+    </row>
+    <row r="258" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B258" s="6"/>
+      <c r="C258" s="6"/>
+      <c r="D258" s="6"/>
+    </row>
+    <row r="259" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B259" s="6"/>
+      <c r="C259" s="6"/>
+      <c r="D259" s="6"/>
+    </row>
+    <row r="260" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B260" s="6"/>
+      <c r="C260" s="10"/>
+      <c r="D260" s="10"/>
+    </row>
+    <row r="261" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B261" s="7"/>
+      <c r="C261" s="7"/>
+      <c r="D261" s="7"/>
+    </row>
+    <row r="262" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B262" s="7"/>
+      <c r="C262" s="7"/>
+      <c r="D262" s="7"/>
+    </row>
+    <row r="263" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B263" s="6"/>
+      <c r="C263" s="7"/>
+      <c r="D263" s="7"/>
+    </row>
+    <row r="264" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B264" s="6"/>
+      <c r="C264" s="7"/>
+      <c r="D264" s="7"/>
+    </row>
+    <row r="265" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B265" s="6"/>
+      <c r="C265" s="6"/>
+      <c r="D265" s="6"/>
+    </row>
+    <row r="266" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B266" s="6"/>
+      <c r="C266" s="6"/>
+      <c r="D266" s="6"/>
+    </row>
+    <row r="267" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B267" s="6"/>
+      <c r="C267" s="10"/>
+      <c r="D267" s="10"/>
+    </row>
+    <row r="268" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B268" s="7"/>
+      <c r="C268" s="7"/>
+      <c r="D268" s="7"/>
+    </row>
+    <row r="269" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B269" s="7"/>
+      <c r="C269" s="7"/>
+      <c r="D269" s="7"/>
+    </row>
+    <row r="270" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B270" s="6"/>
+      <c r="C270" s="7"/>
+      <c r="D270" s="7"/>
+    </row>
+    <row r="271" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B271" s="6"/>
+      <c r="C271" s="7"/>
+      <c r="D271" s="7"/>
+    </row>
+    <row r="272" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B272" s="6"/>
+      <c r="C272" s="6"/>
+      <c r="D272" s="6"/>
+    </row>
+    <row r="273" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B273" s="6"/>
+      <c r="C273" s="6"/>
+      <c r="D273" s="6"/>
+    </row>
+    <row r="274" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B274" s="6"/>
+      <c r="C274" s="10"/>
+      <c r="D274" s="10"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>